--- a/experiments/results/resnet34/CIFAR-10/ReAct+DICE/adaptive/std/results.xlsx
+++ b/experiments/results/resnet34/CIFAR-10/ReAct+DICE/adaptive/std/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -960,6 +960,104 @@
       <c r="O12" s="5" t="inlineStr">
         <is>
           <t>dice_p=85,ash_p=None,react_th=1.0,scale_th=1.0,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>98.47</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>37.87</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>92.52</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>98.52</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>97.17</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>98.44</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=85,ash_p=None,react_th=1.1,scale_th=1.1,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>98.48</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>38.27</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>92.45999999999999</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>98.51000000000001</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>97.13</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>98.42</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>97.48999999999999</v>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=85,ash_p=None,react_th=1.1,scale_th=1.0,type=std</t>
         </is>
       </c>
     </row>
